--- a/public/exports/23795515.xlsx
+++ b/public/exports/23795515.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:L30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tanderupvej 15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2484564</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>275</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pillemarksvej 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2485012</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>449</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pillemarksvej 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2485012</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>515</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pillemarksvej 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2485012</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>362</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvej 3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487601</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>565</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hosebåndet 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">7109104</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>293</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langøre 27</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">743895, 2484343</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>318</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aavej 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2486326</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>256</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">200015682</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-06-23</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søtofte 10</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487133</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>3137</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">311394363</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-22</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 49</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">10114902</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>415</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">311401140</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Onsbjerg Hovedgade 26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2484686</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>466</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">311401141</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Anton Rosens Plads 3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487417</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>343</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">311401518</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-02</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sælvig 64</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">7957729</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>357</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311401517</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-02</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pillemarksvej 1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2485012</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>2219</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311401841</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-03</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marsk Stigs Vej 5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487086</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>1044</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311402281</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marsk Stigs Vej 5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487086</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>918</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311402281</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marsk Stigs Vej 5</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487086</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>2474</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311402281</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marsk Stigs Vej 5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487086</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>947</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311402281</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marsk Stigs Vej 5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487086</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>421</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311402281</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tanderupvej 15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2484564</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>477</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311404607</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-19</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tanderupvej 15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2484564</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>405</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311404606</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-19</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tanderupvej 15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2484564</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>810</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311404710</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-21</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvej 3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2487594</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>614</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311404843</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-22</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildemosen 1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">10114908</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>687</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311655418</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildemosen 2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">10114908</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>687</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311655420</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildemosen 3</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">10114908</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>687</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311655421</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildemosen 4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">10114908</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>687</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311655422</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildemosen 5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">10114908</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>687</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311655423</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,39 +1771,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildemosen 7</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8305</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">10114908</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>721</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311655424</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:L30"/>
 </worksheet>
 </file>
--- a/public/exports/23795515.xlsx
+++ b/public/exports/23795515.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tanderupvej 15</t>
+          <t xml:space="preserve">Hosebåndet 2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2484564</t>
+          <t xml:space="preserve">7109104</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pillemarksvej 1</t>
+          <t xml:space="preserve">Langøre 27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2485012</t>
+          <t xml:space="preserve">743895, 2484343</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>449</v>
+        <v>318</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -226,11 +226,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>515</v>
+        <v>449</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -286,11 +286,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H5">
-        <v>362</v>
+        <v>515</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 3</t>
+          <t xml:space="preserve">Pillemarksvej 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2487601</t>
+          <t xml:space="preserve">2485012</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H6">
-        <v>565</v>
+        <v>362</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hosebåndet 2</t>
+          <t xml:space="preserve">Tanderupvej 15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7109104</t>
+          <t xml:space="preserve">2484564</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H7">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langøre 27</t>
+          <t xml:space="preserve">Tingvej 3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">743895, 2484343</t>
+          <t xml:space="preserve">2487601</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H8">
-        <v>318</v>
+        <v>565</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 49</t>
+          <t xml:space="preserve">Onsbjerg Hovedgade 26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10114902</t>
+          <t xml:space="preserve">2484686</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,11 +650,11 @@
         </is>
       </c>
       <c r="H11">
-        <v>415</v>
+        <v>466</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401140</t>
+          <t xml:space="preserve">311401141</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Onsbjerg Hovedgade 26</t>
+          <t xml:space="preserve">Skolevænget 49</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2484686</t>
+          <t xml:space="preserve">10114902</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -710,11 +710,11 @@
         </is>
       </c>
       <c r="H12">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401141</t>
+          <t xml:space="preserve">311401140</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">

--- a/public/exports/23795515.xlsx
+++ b/public/exports/23795515.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:M30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-23</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-22</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-02</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-02</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-03</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-19</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-19</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-21</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-22</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,21 +1944,26 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-22</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L30"/>
+  <autoFilter ref="A1:M30"/>
 </worksheet>
 </file>